--- a/Tarifario_sctr.xlsx
+++ b/Tarifario_sctr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3EE8C112-3338-4161-9652-BC109B2387C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBC8DD1-DEF7-43CB-B48D-5111E1358358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A800080A-6063-4515-8D0F-5F34B51414F3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tarifario_sctr" sheetId="1" r:id="rId1"/>
     <sheet name="impuestos_minimos" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -74,48 +74,9 @@
     <t>Construcción Civil y Obras</t>
   </si>
   <si>
-    <t>Electricidad de Alta Tensión y Hidrocarburos y Minería</t>
-  </si>
-  <si>
     <t>Impuestos</t>
   </si>
   <si>
-    <t>LIMPIEZA GENERAL DE EDIFICIOS</t>
-  </si>
-  <si>
-    <t>ACTIVIDADES DE SEGURIDAD PRIVADA (ACTIVIDADES DE INVESTIGACIÓN Y SEGURIDAD) (SIN ARMAS)</t>
-  </si>
-  <si>
-    <t>ACTIVIDADES DE ARQUITECTURA E INGENIERIA Y ACTIVIDADES CONEXAS DE CONSULTORIA TE...</t>
-  </si>
-  <si>
-    <t>MANTENIMIENTO Y REPARACIÓN DE VEHÍCULOS AUTOMOTORES</t>
-  </si>
-  <si>
-    <t>ACTIVIDADES DE TELECOMUNICACIONES ALÁMBRICAS</t>
-  </si>
-  <si>
-    <t>ACTIVIDADES DE HOSPITALES</t>
-  </si>
-  <si>
-    <t>OTRAS ACTIVIDADES DE ATENCIÓN DE LA SALUD HUMANA</t>
-  </si>
-  <si>
-    <t>ACTIVIDADES VETERINARIAS</t>
-  </si>
-  <si>
-    <t>TRANSPORTE DE CARGA POR CARRETERA</t>
-  </si>
-  <si>
-    <t>MANIPULACIÓN DE LA CARGA</t>
-  </si>
-  <si>
-    <t>FABRICACIÓN DE PRODUCTOS METÁLICOS PARA USO ESTRUCTURAL</t>
-  </si>
-  <si>
-    <t>GENERACIÓN, TRANSMISIÓN Y DISTRIBUCIÓN DE ENERGÍA ELÉCTRICA</t>
-  </si>
-  <si>
     <t>Concepto</t>
   </si>
   <si>
@@ -125,7 +86,46 @@
     <t>Prima Minima Emision</t>
   </si>
   <si>
-    <t>CONSTRUCCIÓN DE EDIFICIOS, OBRAS DE INGENIERÍA CIVIL, DEMOLICIÓN Y ACABADOS</t>
+    <t>Electricidad de Alta Tensión y Hidrocarburos</t>
+  </si>
+  <si>
+    <t>Limpieza general de edificios</t>
+  </si>
+  <si>
+    <t>Actividades de seguridad privada (actividades de investigación y seguridad) (sin armas)</t>
+  </si>
+  <si>
+    <t>Actividades de arquitectura e ingenieria y actividades conexas de consultoria te...</t>
+  </si>
+  <si>
+    <t>Mantenimiento y reparación de vehículos automotores</t>
+  </si>
+  <si>
+    <t>Actividades de telecomunicaciones alámbricas</t>
+  </si>
+  <si>
+    <t>Actividades de hospitales</t>
+  </si>
+  <si>
+    <t>Otras actividades de atención de la salud humana</t>
+  </si>
+  <si>
+    <t>Actividades veterinarias</t>
+  </si>
+  <si>
+    <t>Transporte de carga por carretera</t>
+  </si>
+  <si>
+    <t>Manipulación de la carga</t>
+  </si>
+  <si>
+    <t>Fabricación de productos metálicos para uso estructural</t>
+  </si>
+  <si>
+    <t>Construcción de edificios, obras de ingeniería civil, demolición y acabados</t>
+  </si>
+  <si>
+    <t>Generación, transmisión y distribución de energía eléctrica</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1012,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2">
         <v>0.97</v>
@@ -1044,7 +1044,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>1.46</v>
@@ -1076,7 +1076,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>0.8</v>
@@ -1108,7 +1108,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0.56999999999999995</v>
@@ -1140,7 +1140,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>1.5</v>
@@ -1172,7 +1172,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0.82</v>
@@ -1204,7 +1204,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>0.98</v>
@@ -1230,7 +1230,7 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>0.98</v>
@@ -1256,7 +1256,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>2.73</v>
@@ -1282,7 +1282,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E11">
         <v>1.19</v>
@@ -1308,7 +1308,7 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12">
         <v>2.73</v>
@@ -1334,7 +1334,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13">
         <v>1.1599999999999999</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E14">
         <v>2.1800000000000002</v>
@@ -1393,7 +1393,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1">
         <v>0.18</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>60</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>30</v>

--- a/Tarifario_sctr.xlsx
+++ b/Tarifario_sctr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBC8DD1-DEF7-43CB-B48D-5111E1358358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCF9167-3C88-4982-A4E0-44DD1F8191C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A800080A-6063-4515-8D0F-5F34B51414F3}"/>
+    <workbookView xWindow="-24225" yWindow="4065" windowWidth="21585" windowHeight="11385" xr2:uid="{A800080A-6063-4515-8D0F-5F34B51414F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifario_sctr" sheetId="1" r:id="rId1"/>
@@ -1206,6 +1206,12 @@
       <c r="B8" t="s">
         <v>28</v>
       </c>
+      <c r="C8">
+        <v>0.53</v>
+      </c>
+      <c r="D8">
+        <v>0.82</v>
+      </c>
       <c r="E8">
         <v>0.98</v>
       </c>
@@ -1232,6 +1238,12 @@
       <c r="B9" t="s">
         <v>29</v>
       </c>
+      <c r="C9">
+        <v>0.44</v>
+      </c>
+      <c r="D9">
+        <v>0.43</v>
+      </c>
       <c r="E9">
         <v>0.98</v>
       </c>
@@ -1258,6 +1270,12 @@
       <c r="B10" t="s">
         <v>30</v>
       </c>
+      <c r="C10">
+        <v>1.18</v>
+      </c>
+      <c r="D10">
+        <v>1.57</v>
+      </c>
       <c r="E10">
         <v>2.73</v>
       </c>
@@ -1284,6 +1302,12 @@
       <c r="B11" t="s">
         <v>31</v>
       </c>
+      <c r="C11">
+        <v>1.18</v>
+      </c>
+      <c r="D11">
+        <v>1.57</v>
+      </c>
       <c r="E11">
         <v>1.19</v>
       </c>
@@ -1310,6 +1334,12 @@
       <c r="B12" t="s">
         <v>32</v>
       </c>
+      <c r="C12">
+        <v>1.03</v>
+      </c>
+      <c r="D12">
+        <v>1.33</v>
+      </c>
       <c r="E12">
         <v>2.73</v>
       </c>
@@ -1336,6 +1366,12 @@
       <c r="B13" t="s">
         <v>33</v>
       </c>
+      <c r="C13">
+        <v>1.06</v>
+      </c>
+      <c r="D13">
+        <v>1.62</v>
+      </c>
       <c r="E13">
         <v>1.1599999999999999</v>
       </c>
@@ -1361,6 +1397,12 @@
       </c>
       <c r="B14" t="s">
         <v>34</v>
+      </c>
+      <c r="C14">
+        <v>1.01</v>
+      </c>
+      <c r="D14">
+        <v>1.17</v>
       </c>
       <c r="E14">
         <v>2.1800000000000002</v>
